--- a/teams-and-rosters/CS320-Sp25-101-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-101-roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9359FB3-6FC3-4F87-83C4-294D1D26299E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB0F1DE-3EFB-4A8A-932F-6600C56F0D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1935" windowWidth="21480" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="1440" windowWidth="11490" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-101-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Major</t>
   </si>
@@ -48,15 +48,6 @@
   </si>
   <si>
     <t>CS320 Section 101: M-W-F  2:00p to 2:50p</t>
-  </si>
-  <si>
-    <t>Buler</t>
-  </si>
-  <si>
-    <t>Aleksandar</t>
-  </si>
-  <si>
-    <t>UND</t>
   </si>
   <si>
     <t>SO</t>
@@ -480,7 +471,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -640,19 +631,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -698,7 +676,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -712,10 +690,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1082,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -1092,40 +1066,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="10"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1137,10 +1111,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -1152,10 +1126,10 @@
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -1167,146 +1141,138 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1316,21 +1282,14 @@
       <c r="D16" s="4"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/teams-and-rosters/CS320-Sp25-101-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-101-roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB0F1DE-3EFB-4A8A-932F-6600C56F0D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA824586-3619-44A3-8B90-5BBB1D2E0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="1440" windowWidth="11490" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="1245" windowWidth="11205" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-101-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>Major</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Hanna</t>
   </si>
   <si>
-    <t>Joshua</t>
-  </si>
-  <si>
     <t>CS</t>
   </si>
   <si>
@@ -125,7 +122,16 @@
     <t>Zink</t>
   </si>
   <si>
-    <t>Joseph</t>
+    <t>Natale</t>
+  </si>
+  <si>
+    <t>Evan</t>
+  </si>
+  <si>
+    <t>Nadia</t>
+  </si>
+  <si>
+    <t>Jos</t>
   </si>
 </sst>
 </file>
@@ -1093,10 +1099,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
@@ -1105,43 +1111,43 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
@@ -1150,28 +1156,28 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>5</v>
@@ -1180,58 +1186,58 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>5</v>
@@ -1240,13 +1246,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>5</v>
@@ -1255,13 +1261,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>5</v>
@@ -1269,10 +1275,18 @@
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">

--- a/teams-and-rosters/CS320-Sp25-101-roster.xlsx
+++ b/teams-and-rosters/CS320-Sp25-101-roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2025\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA824586-3619-44A3-8B90-5BBB1D2E0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE63871F-93B8-460F-9DE6-5FDAEC588633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1245" windowWidth="11205" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="20790" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cs320-101-sp25-roster" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>Nadia</t>
   </si>
   <si>
-    <t>Jos</t>
+    <t>Joe</t>
   </si>
 </sst>
 </file>
